--- a/Design Files/Main-Board-v1.0/BOM/JLCPCB-BOM-Main Board - v1.0.xlsx
+++ b/Design Files/Main-Board-v1.0/BOM/JLCPCB-BOM-Main Board - v1.0.xlsx
@@ -132,7 +132,7 @@
     <t>R3</t>
   </si>
   <si>
-    <t>R4, R5, R6, R8, R9, R10</t>
+    <t>R4, R5, R6, R8, R9, R10, R12</t>
   </si>
   <si>
     <t>R7, R11</t>

--- a/Design Files/Main-Board-v1.0/BOM/JLCPCB-BOM-Main Board - v1.0.xlsx
+++ b/Design Files/Main-Board-v1.0/BOM/JLCPCB-BOM-Main Board - v1.0.xlsx
@@ -51,9 +51,6 @@
     <t>HC-1.25-3PLT</t>
   </si>
   <si>
-    <t>SM04B-SRSS-TB(LF)(SN)</t>
-  </si>
-  <si>
     <t>SM03B-SRSS-TB(LF)(SN)</t>
   </si>
   <si>
@@ -222,9 +219,6 @@
     <t>C2845389</t>
   </si>
   <si>
-    <t>C160404</t>
-  </si>
-  <si>
     <t>C160403</t>
   </si>
   <si>
@@ -256,6 +250,12 @@
   </si>
   <si>
     <t>C20625731</t>
+  </si>
+  <si>
+    <t>C7430446</t>
+  </si>
+  <si>
+    <t>ZX-SH1.0-4PWT</t>
   </si>
 </sst>
 </file>
@@ -715,13 +715,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -729,13 +729,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -743,13 +743,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -757,13 +757,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -771,13 +771,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -785,13 +785,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -799,13 +799,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -813,13 +813,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -827,13 +827,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>8</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -841,181 +841,181 @@
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>10</v>
+        <v>78</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>10</v>
+        <v>78</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
